--- a/weeks/◆ 2026년 10월 3주 편성표 (1012 ~ 1018) (1).xlsx
+++ b/weeks/◆ 2026년 10월 3주 편성표 (1012 ~ 1018) (1).xlsx
@@ -462,13 +462,13 @@
     <xf numFmtId="49" fontId="32" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="49" fontId="33" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -485,48 +485,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.25"/>
-    <col min="3" max="3" customWidth="true" width="3.75"/>
-    <col min="4" max="4" customWidth="true" width="2.625"/>
-    <col min="5" max="5" customWidth="true" width="1.5"/>
-    <col min="6" max="6" customWidth="true" width="2.625"/>
-    <col min="7" max="7" customWidth="true" width="11.875"/>
-    <col min="8" max="8" customWidth="true" width="0.25"/>
-    <col min="9" max="9" customWidth="true" width="3.75"/>
-    <col min="10" max="10" customWidth="true" width="2.625"/>
-    <col min="11" max="11" customWidth="true" width="1.5"/>
-    <col min="12" max="12" customWidth="true" width="2.625"/>
-    <col min="13" max="13" customWidth="true" width="11.875"/>
-    <col min="14" max="14" customWidth="true" width="0.25"/>
-    <col min="15" max="15" customWidth="true" width="3.75"/>
-    <col min="16" max="16" customWidth="true" width="2.625"/>
-    <col min="17" max="17" customWidth="true" width="1.5"/>
-    <col min="18" max="18" customWidth="true" width="2.625"/>
-    <col min="19" max="19" customWidth="true" width="11.875"/>
-    <col min="20" max="20" customWidth="true" width="0.25"/>
-    <col min="21" max="21" customWidth="true" width="3.75"/>
-    <col min="22" max="22" customWidth="true" width="2.625"/>
-    <col min="23" max="23" customWidth="true" width="1.5"/>
-    <col min="24" max="24" customWidth="true" width="2.625"/>
-    <col min="25" max="25" customWidth="true" width="11.875"/>
-    <col min="26" max="26" customWidth="true" width="0.25"/>
-    <col min="27" max="27" customWidth="true" width="3.75"/>
-    <col min="28" max="28" customWidth="true" width="2.625"/>
-    <col min="29" max="29" customWidth="true" width="1.5"/>
-    <col min="30" max="30" customWidth="true" width="2.625"/>
-    <col min="31" max="31" customWidth="true" width="11.875"/>
-    <col min="32" max="32" customWidth="true" width="0.25"/>
-    <col min="33" max="33" customWidth="true" width="3.75"/>
-    <col min="34" max="34" customWidth="true" width="2.625"/>
-    <col min="35" max="35" customWidth="true" width="1.5"/>
-    <col min="36" max="36" customWidth="true" width="2.625"/>
-    <col min="37" max="37" customWidth="true" width="11.875"/>
-    <col min="38" max="38" customWidth="true" width="0.25"/>
-    <col min="39" max="39" customWidth="true" width="3.75"/>
-    <col min="40" max="40" customWidth="true" width="2.625"/>
-    <col min="41" max="41" customWidth="true" width="1.5"/>
-    <col min="42" max="42" customWidth="true" width="2.625"/>
-    <col min="43" max="43" customWidth="true" width="11.625"/>
+    <col min="2" max="2" customWidth="true" width="0.375"/>
+    <col min="3" max="3" customWidth="true" width="5.125"/>
+    <col min="4" max="4" customWidth="true" width="3.625"/>
+    <col min="5" max="5" customWidth="true" width="2.125"/>
+    <col min="6" max="6" customWidth="true" width="3.625"/>
+    <col min="7" max="7" customWidth="true" width="16.375"/>
+    <col min="8" max="8" customWidth="true" width="0.375"/>
+    <col min="9" max="9" customWidth="true" width="5.125"/>
+    <col min="10" max="10" customWidth="true" width="3.625"/>
+    <col min="11" max="11" customWidth="true" width="2.125"/>
+    <col min="12" max="12" customWidth="true" width="3.625"/>
+    <col min="13" max="13" customWidth="true" width="16.375"/>
+    <col min="14" max="14" customWidth="true" width="0.375"/>
+    <col min="15" max="15" customWidth="true" width="5.125"/>
+    <col min="16" max="16" customWidth="true" width="3.625"/>
+    <col min="17" max="17" customWidth="true" width="2.125"/>
+    <col min="18" max="18" customWidth="true" width="3.625"/>
+    <col min="19" max="19" customWidth="true" width="16.375"/>
+    <col min="20" max="20" customWidth="true" width="0.375"/>
+    <col min="21" max="21" customWidth="true" width="5.125"/>
+    <col min="22" max="22" customWidth="true" width="3.625"/>
+    <col min="23" max="23" customWidth="true" width="2.125"/>
+    <col min="24" max="24" customWidth="true" width="3.625"/>
+    <col min="25" max="25" customWidth="true" width="16.375"/>
+    <col min="26" max="26" customWidth="true" width="0.375"/>
+    <col min="27" max="27" customWidth="true" width="5.125"/>
+    <col min="28" max="28" customWidth="true" width="3.625"/>
+    <col min="29" max="29" customWidth="true" width="2.125"/>
+    <col min="30" max="30" customWidth="true" width="3.625"/>
+    <col min="31" max="31" customWidth="true" width="16.375"/>
+    <col min="32" max="32" customWidth="true" width="0.375"/>
+    <col min="33" max="33" customWidth="true" width="5.125"/>
+    <col min="34" max="34" customWidth="true" width="3.625"/>
+    <col min="35" max="35" customWidth="true" width="2.125"/>
+    <col min="36" max="36" customWidth="true" width="3.625"/>
+    <col min="37" max="37" customWidth="true" width="16.375"/>
+    <col min="38" max="38" customWidth="true" width="0.375"/>
+    <col min="39" max="39" customWidth="true" width="5.125"/>
+    <col min="40" max="40" customWidth="true" width="3.625"/>
+    <col min="41" max="41" customWidth="true" width="2.125"/>
+    <col min="42" max="42" customWidth="true" width="3.625"/>
+    <col min="43" max="43" customWidth="true" width="16.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -573,7 +573,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>2차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="L11" s="30" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
+          <t>'패션4Lab'</t>
         </is>
       </c>
       <c r="M11" s="30" t="inlineStr">
         <is>
-          <t>머티리얼랩 스웨디드 코튼100 타탄체크 셔켓 外</t>
+          <t>라우라비아조티 울블렌디드 팬츠 1종</t>
         </is>
       </c>
       <c r="N11" s="25"/>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="X12" s="30" t="inlineStr">
         <is>
-          <t>'패션4Lab'</t>
+          <t>'패션3Lab'</t>
         </is>
       </c>
       <c r="Y12" s="30" t="inlineStr">
         <is>
-          <t>라우라비아조티 울블렌디드 팬츠 1종</t>
+          <t>머티리얼랩 스웨디드 코튼100 타탄체크 셔켓 外</t>
         </is>
       </c>
       <c r="Z12" s="25"/>
@@ -2082,7 +2082,7 @@
           <t>11:35</t>
         </is>
       </c>
-      <c r="V14" s="38" t="inlineStr">
+      <c r="V14" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2097,7 +2097,7 @@
           <t>'패션4Lab'</t>
         </is>
       </c>
-      <c r="Y14" s="39" t="inlineStr">
+      <c r="Y14" s="30" t="inlineStr">
         <is>
           <t>정호진 트렌치코트</t>
         </is>
@@ -2209,7 +2209,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G15" s="40" t="inlineStr">
+      <c r="G15" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2268,12 +2268,12 @@
         </is>
       </c>
       <c r="T15" s="25"/>
-      <c r="U15" s="29" t="inlineStr">
+      <c r="U15" s="36" t="inlineStr">
         <is>
           <t>12:25</t>
         </is>
       </c>
-      <c r="V15" s="38" t="inlineStr">
+      <c r="V15" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="X15" s="30" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
-        </is>
-      </c>
-      <c r="Y15" s="39" t="inlineStr">
-        <is>
-          <t>이상봉 숄더백 라지</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="Y15" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="Z15" s="25"/>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B16" s="25"/>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>13:25</t>
         </is>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G16" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션2Lab'</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>이상봉 숄더백 라지</t>
         </is>
       </c>
       <c r="H16" s="25"/>
@@ -2426,7 +2426,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M16" s="40" t="inlineStr">
+      <c r="M16" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2506,7 +2506,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AE16" s="40" t="inlineStr">
+      <c r="AE16" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="AI17" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AJ17" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="AK17" s="40" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="AK17" s="30" t="inlineStr">
+        <is>
+          <t>캐롤프랑크 아이크림</t>
         </is>
       </c>
       <c r="AL17" s="25"/>
@@ -2798,7 +2798,7 @@
           <t>14:55</t>
         </is>
       </c>
-      <c r="J18" s="38" t="inlineStr">
+      <c r="J18" s="39" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2814,7 +2814,7 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="M18" s="39" t="inlineStr">
+      <c r="M18" s="40" t="inlineStr">
         <is>
           <t>LG 냉장고</t>
         </is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="Z18" s="25"/>
-      <c r="AA18" s="36" t="inlineStr">
+      <c r="AA18" s="29" t="inlineStr">
         <is>
           <t>14:35</t>
         </is>
@@ -2883,19 +2883,20 @@
           <t>55</t>
         </is>
       </c>
-      <c r="AC18" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="AC18" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AD18" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE18" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AE18" s="30" t="inlineStr">
+        <is>
+          <t>에버홈 믹서기</t>
         </is>
       </c>
       <c r="AF18" s="25"/>
@@ -2911,17 +2912,17 @@
       </c>
       <c r="AI18" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AJ18" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="AK18" s="30" t="inlineStr">
-        <is>
-          <t>캐롤프랑크 아이크림</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AK18" s="38" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="AL18" s="25"/>
@@ -2979,7 +2980,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="G19" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2990,7 +2991,7 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="J19" s="38" t="inlineStr">
+      <c r="J19" s="39" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -3006,9 +3007,9 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="M19" s="39" t="inlineStr">
-        <is>
-          <t>LG 건조기</t>
+      <c r="M19" s="40" t="inlineStr">
+        <is>
+          <t>LG TV</t>
         </is>
       </c>
       <c r="N19" s="25"/>
@@ -3635,7 +3636,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="Y22" s="40" t="inlineStr">
+      <c r="Y22" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -4100,7 +4101,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AQ24" s="40" t="inlineStr">
+      <c r="AQ24" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -4352,7 +4353,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M26" s="40" t="inlineStr">
+      <c r="M26" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -4560,7 +4561,7 @@
         </is>
       </c>
       <c r="T27" s="25"/>
-      <c r="U27" s="29" t="inlineStr">
+      <c r="U27" s="36" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4577,12 +4578,12 @@
       </c>
       <c r="X27" s="30" t="inlineStr">
         <is>
-          <t>'패션1Lab'</t>
-        </is>
-      </c>
-      <c r="Y27" s="30" t="inlineStr">
-        <is>
-          <t>로얄메르 셋업</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="Y27" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="Z27" s="25"/>
@@ -4632,7 +4633,7 @@
           <t>'GA'</t>
         </is>
       </c>
-      <c r="AK27" s="40" t="inlineStr">
+      <c r="AK27" s="38" t="inlineStr">
         <is>
           <t>#금융GA</t>
         </is>
@@ -4675,13 +4676,13 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G28" s="40" t="inlineStr">
+      <c r="G28" s="38" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="H28" s="25"/>
-      <c r="I28" s="36" t="inlineStr">
+      <c r="I28" s="29" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4698,12 +4699,12 @@
       </c>
       <c r="L28" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M28" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션1Lab'</t>
+        </is>
+      </c>
+      <c r="M28" s="30" t="inlineStr">
+        <is>
+          <t>로얄메르 셋업</t>
         </is>
       </c>
       <c r="N28" s="25"/>
